--- a/basedatos_partidas/salida/descompuestos/05.07.01.040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/05.07.01.040.xlsx
@@ -636,7 +636,7 @@
         <v>0.014</v>
       </c>
       <c r="G13" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
         <v>0.07000000000000001</v>
